--- a/parser/data/xlsx/ml_experiments.xlsx
+++ b/parser/data/xlsx/ml_experiments.xlsx
@@ -627,12 +627,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0a05cb32-2700-44d7-b6c8-e69700564f6f</t>
+          <t>393be70b-2760-4402-b968-a900df46a52e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T16:56:45.537621</t>
+          <t>2026-02-25T17:23:32.637210</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_c24603f2_final.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_0b0ba787_final.csv</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -731,21 +731,21 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.203170100023272</v>
+        <v>1.326650300004985</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\data_preprocessed_1_c24603f2_final\data_preprocessed_1_c24603f2_final_20260225_165645.joblib</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\data_preprocessed_1_0b0ba787_final\data_preprocessed_1_0b0ba787_final_20260225_172332.joblib</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\data_preprocessed_1_c24603f2_final</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\data_preprocessed_1_0b0ba787_final</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>data_preprocessed_1_c24603f2_final_20260225_165645.joblib</t>
+          <t>data_preprocessed_1_0b0ba787_final_20260225_172332.joblib</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">

--- a/parser/data/xlsx/ml_experiments.xlsx
+++ b/parser/data/xlsx/ml_experiments.xlsx
@@ -627,12 +627,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>393be70b-2760-4402-b968-a900df46a52e</t>
+          <t>d2991275-8bd1-4891-9a74-05fac8c1f674</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T17:23:32.637210</t>
+          <t>2026-02-25T18:04:21.585772</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_0b0ba787_final.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_7ee3ce34_final.csv</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -731,21 +731,21 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.326650300004985</v>
+        <v>1.267070799978683</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\data_preprocessed_1_0b0ba787_final\data_preprocessed_1_0b0ba787_final_20260225_172332.joblib</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\data_preprocessed_1_7ee3ce34_final\data_preprocessed_1_7ee3ce34_final_20260225_180421.joblib</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\data_preprocessed_1_0b0ba787_final</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\data_preprocessed_1_7ee3ce34_final</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>data_preprocessed_1_0b0ba787_final_20260225_172332.joblib</t>
+          <t>data_preprocessed_1_7ee3ce34_final_20260225_180421.joblib</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">

--- a/parser/data/xlsx/ml_experiments.xlsx
+++ b/parser/data/xlsx/ml_experiments.xlsx
@@ -445,7 +445,7 @@
     <col width="41" customWidth="1" min="27" max="27"/>
     <col width="20" customWidth="1" min="28" max="28"/>
     <col width="20" customWidth="1" min="29" max="29"/>
-    <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="19" customWidth="1" min="30" max="30"/>
     <col width="173" customWidth="1" min="31" max="31"/>
     <col width="115" customWidth="1" min="32" max="32"/>
     <col width="59" customWidth="1" min="33" max="33"/>
@@ -627,12 +627,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d2991275-8bd1-4891-9a74-05fac8c1f674</t>
+          <t>0cdce9cb-7efe-4ba2-b745-2071ff6b7348</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T18:04:21.585772</t>
+          <t>2026-02-26T13:48:53.592167</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_7ee3ce34_final.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_ca031a75_final.csv</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -731,21 +731,21 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.267070799978683</v>
+        <v>1.609604400000535</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\data_preprocessed_1_7ee3ce34_final\data_preprocessed_1_7ee3ce34_final_20260225_180421.joblib</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\data_preprocessed_1_ca031a75_final\data_preprocessed_1_ca031a75_final_20260226_134853.joblib</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\data_preprocessed_1_7ee3ce34_final</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\data_preprocessed_1_ca031a75_final</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>data_preprocessed_1_7ee3ce34_final_20260225_180421.joblib</t>
+          <t>data_preprocessed_1_ca031a75_final_20260226_134853.joblib</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">

--- a/parser/data/xlsx/ml_experiments.xlsx
+++ b/parser/data/xlsx/ml_experiments.xlsx
@@ -424,7 +424,7 @@
     <col width="29" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="31" customWidth="1" min="8" max="8"/>
-    <col width="109" customWidth="1" min="9" max="9"/>
+    <col width="137" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
@@ -445,10 +445,10 @@
     <col width="41" customWidth="1" min="27" max="27"/>
     <col width="20" customWidth="1" min="28" max="28"/>
     <col width="20" customWidth="1" min="29" max="29"/>
-    <col width="19" customWidth="1" min="30" max="30"/>
-    <col width="173" customWidth="1" min="31" max="31"/>
-    <col width="115" customWidth="1" min="32" max="32"/>
-    <col width="59" customWidth="1" min="33" max="33"/>
+    <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="229" customWidth="1" min="31" max="31"/>
+    <col width="143" customWidth="1" min="32" max="32"/>
+    <col width="87" customWidth="1" min="33" max="33"/>
     <col width="17" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
@@ -627,12 +627,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0cdce9cb-7efe-4ba2-b745-2071ff6b7348</t>
+          <t>bb008549-d3df-465d-acd7-b232b9420c64</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-26T13:48:53.592167</t>
+          <t>2026-02-26T14:46:13.793732</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_ca031a75_final.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\7abc486a8f2944fab510c38389cbf6f4_preprocessed_1_733e1348_final.csv</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -731,21 +731,21 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.609604400000535</v>
+        <v>1.502410600020085</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\data_preprocessed_1_ca031a75_final\data_preprocessed_1_ca031a75_final_20260226_134853.joblib</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\7abc486a8f2944fab510c38389cbf6f4_preprocessed_1_733e1348_final\7abc486a8f2944fab510c38389cbf6f4_preprocessed_1_733e1348_final_20260226_144613.joblib</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\data_preprocessed_1_ca031a75_final</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\7abc486a8f2944fab510c38389cbf6f4_preprocessed_1_733e1348_final</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>data_preprocessed_1_ca031a75_final_20260226_134853.joblib</t>
+          <t>7abc486a8f2944fab510c38389cbf6f4_preprocessed_1_733e1348_final_20260226_144613.joblib</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">

--- a/parser/data/xlsx/ml_experiments.xlsx
+++ b/parser/data/xlsx/ml_experiments.xlsx
@@ -627,12 +627,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bb008549-d3df-465d-acd7-b232b9420c64</t>
+          <t>3c8d9aba-e747-404c-93ba-1598590ce4e9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-26T14:46:13.793732</t>
+          <t>2026-02-26T14:55:28.216907</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\7abc486a8f2944fab510c38389cbf6f4_preprocessed_1_733e1348_final.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\5a6b5300428640cbaae38090de224504_preprocessed_1_8061a7e4_final.csv</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -731,21 +731,21 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.502410600020085</v>
+        <v>1.578005200019106</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\7abc486a8f2944fab510c38389cbf6f4_preprocessed_1_733e1348_final\7abc486a8f2944fab510c38389cbf6f4_preprocessed_1_733e1348_final_20260226_144613.joblib</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\5a6b5300428640cbaae38090de224504_preprocessed_1_8061a7e4_final\5a6b5300428640cbaae38090de224504_preprocessed_1_8061a7e4_final_20260226_145527.joblib</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\7abc486a8f2944fab510c38389cbf6f4_preprocessed_1_733e1348_final</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\5a6b5300428640cbaae38090de224504_preprocessed_1_8061a7e4_final</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>7abc486a8f2944fab510c38389cbf6f4_preprocessed_1_733e1348_final_20260226_144613.joblib</t>
+          <t>5a6b5300428640cbaae38090de224504_preprocessed_1_8061a7e4_final_20260226_145527.joblib</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">

--- a/parser/data/xlsx/ml_experiments.xlsx
+++ b/parser/data/xlsx/ml_experiments.xlsx
@@ -413,344 +413,620 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AP4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="29" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="31" customWidth="1" min="8" max="8"/>
-    <col width="137" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="143" customWidth="1" min="1" max="1"/>
+    <col width="87" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="229" customWidth="1" min="4" max="4"/>
+    <col width="137" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="39" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="66" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="66" customWidth="1" min="13" max="13"/>
-    <col width="39" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
-    <col width="33" customWidth="1" min="16" max="16"/>
-    <col width="47" customWidth="1" min="17" max="17"/>
-    <col width="44" customWidth="1" min="18" max="18"/>
-    <col width="51" customWidth="1" min="19" max="19"/>
-    <col width="47" customWidth="1" min="20" max="20"/>
-    <col width="41" customWidth="1" min="21" max="21"/>
-    <col width="47" customWidth="1" min="22" max="22"/>
-    <col width="42" customWidth="1" min="23" max="23"/>
-    <col width="26" customWidth="1" min="24" max="24"/>
-    <col width="36" customWidth="1" min="25" max="25"/>
-    <col width="41" customWidth="1" min="26" max="26"/>
-    <col width="41" customWidth="1" min="27" max="27"/>
-    <col width="20" customWidth="1" min="28" max="28"/>
-    <col width="20" customWidth="1" min="29" max="29"/>
-    <col width="20" customWidth="1" min="30" max="30"/>
-    <col width="229" customWidth="1" min="31" max="31"/>
-    <col width="143" customWidth="1" min="32" max="32"/>
-    <col width="87" customWidth="1" min="33" max="33"/>
-    <col width="17" customWidth="1" min="34" max="34"/>
+    <col width="38" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="41" customWidth="1" min="14" max="14"/>
+    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="41" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="31" customWidth="1" min="18" max="18"/>
+    <col width="44" customWidth="1" min="19" max="19"/>
+    <col width="32" customWidth="1" min="20" max="20"/>
+    <col width="27" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="44" customWidth="1" min="24" max="24"/>
+    <col width="47" customWidth="1" min="25" max="25"/>
+    <col width="51" customWidth="1" min="26" max="26"/>
+    <col width="45" customWidth="1" min="27" max="27"/>
+    <col width="47" customWidth="1" min="28" max="28"/>
+    <col width="41" customWidth="1" min="29" max="29"/>
+    <col width="41" customWidth="1" min="30" max="30"/>
+    <col width="47" customWidth="1" min="31" max="31"/>
+    <col width="42" customWidth="1" min="32" max="32"/>
+    <col width="33" customWidth="1" min="33" max="33"/>
+    <col width="31" customWidth="1" min="34" max="34"/>
+    <col width="30" customWidth="1" min="35" max="35"/>
+    <col width="28" customWidth="1" min="36" max="36"/>
+    <col width="29" customWidth="1" min="37" max="37"/>
+    <col width="17" customWidth="1" min="38" max="38"/>
+    <col width="16" customWidth="1" min="39" max="39"/>
+    <col width="28" customWidth="1" min="40" max="40"/>
+    <col width="20" customWidth="1" min="41" max="41"/>
+    <col width="26" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>artifact_directory</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>artifact_filename</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>artifact_format</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>artifact_path</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>dataset_path</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>dataset_profile_class_distribution</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>dataset_profile_class_distribution_No</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>dataset_profile_class_distribution_Yes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>dataset_profile_dataset_hash</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>dataset_profile_n_features</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>dataset_profile_n_rows</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>experiment_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>metrics_classification</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>metrics_classification_confusion_matrix</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>metrics_classification_train_score</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>metrics_classification_validation_score</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>metrics_clustering</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>metrics_clustering_n_clusters</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>metrics_clustering_n_numeric_features_used</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>metrics_clustering_noise_ratio</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>metrics_clustering_status</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>metrics_regression</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>model_initialization_init_params_max_depth</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>model_initialization_init_params_max_features</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>model_initialization_init_params_min_samples_leaf</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>model_initialization_init_params_n_clusters</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>model_initialization_init_params_n_estimators</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>model_initialization_init_params_n_init</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>model_initialization_init_params_n_jobs</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>model_initialization_init_params_random_state</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>model_initialization_initializer_version</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>model_initialization_model_name</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>runtime_model_estimator_class</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>runtime_model_estimator_type</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>runtime_model_model_family</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>runtime_model_model_variant</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>target_column</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>task</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>task</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>runtime_model_model_family</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>runtime_model_model_variant</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>runtime_model_estimator_type</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>runtime_model_estimator_class</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>dataset_path</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>target_column</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>dataset_profile_n_rows</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>dataset_profile_n_features</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>dataset_profile_dataset_hash</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>dataset_profile_class_distribution_No</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>dataset_profile_class_distribution_Yes</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>model_initialization_model_name</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>model_initialization_init_params_n_estimators</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>model_initialization_init_params_max_depth</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>model_initialization_init_params_min_samples_leaf</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>model_initialization_init_params_max_features</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>model_initialization_init_params_n_jobs</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>model_initialization_init_params_random_state</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>model_initialization_initializer_version</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>training_time_sec</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
         <is>
           <t>validation_strategy_type</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>metrics_classification_train_score</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>metrics_classification_validation_score</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>metrics_classification_confusion_matrix</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>metrics_regression</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>metrics_clustering</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>training_time_sec</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>artifact_path</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>artifact_directory</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>artifact_filename</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>artifact_format</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3c8d9aba-e747-404c-93ba-1598590ce4e9</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\5a6b5300428640cbaae38090de224504_preprocessed_1_8061a7e4_final</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-26T14:55:28.216907</t>
+          <t>5a6b5300428640cbaae38090de224504_preprocessed_1_8061a7e4_final_20260226_145527.joblib</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>joblib</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\5a6b5300428640cbaae38090de224504_preprocessed_1_8061a7e4_final\5a6b5300428640cbaae38090de224504_preprocessed_1_8061a7e4_final_20260226_145527.joblib</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>random_forest</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>random_forest_classifier</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>classifier</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>RandomForestClassifier</t>
-        </is>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\5a6b5300428640cbaae38090de224504_preprocessed_1_8061a7e4_final.csv</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8586</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.1414</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\5a6b5300428640cbaae38090de224504_preprocessed_1_8061a7e4_final.csv</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>CustomerChurned</t>
-        </is>
+          <t>6652df7b89b72022be2c87d5102a29d57c62ce050337750a69d24fbaad59950a</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>17</v>
       </c>
       <c r="K2" t="n">
         <v>5000</v>
       </c>
-      <c r="L2" t="n">
-        <v>17</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>6652df7b89b72022be2c87d5102a29d57c62ce050337750a69d24fbaad59950a</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>0.8586</v>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>3c8d9aba-e747-404c-93ba-1598590ce4e9</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>[848, 13], [37, 102]</t>
+        </is>
       </c>
       <c r="O2" t="n">
-        <v>0.1414</v>
-      </c>
-      <c r="P2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>random_forest</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="Z2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="n">
         <v>150</v>
       </c>
-      <c r="S2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="n">
+      <c r="AD2" t="n">
         <v>-1</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AE2" t="n">
         <v>42</v>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>random_forest</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>classifier</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>random_forest</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>random_forest_classifier</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>CustomerChurned</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>2026-02-26T14:55:28.216907</t>
+        </is>
+      </c>
+      <c r="AO2" t="n">
+        <v>1.578005200019106</v>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>holdout</t>
         </is>
       </c>
-      <c r="Y2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>[848, 13], [37, 102]</t>
-        </is>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.578005200019106</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\5a6b5300428640cbaae38090de224504_preprocessed_1_8061a7e4_final\5a6b5300428640cbaae38090de224504_preprocessed_1_8061a7e4_final_20260226_145527.joblib</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\5a6b5300428640cbaae38090de224504_preprocessed_1_8061a7e4_final</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>5a6b5300428640cbaae38090de224504_preprocessed_1_8061a7e4_final_20260226_145527.joblib</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\data_preprocessed_1_c13340b5_final</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>data_preprocessed_1_c13340b5_final_20260227_140905.joblib</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>joblib</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\data_preprocessed_1_c13340b5_final\data_preprocessed_1_c13340b5_final_20260227_140905.joblib</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_c13340b5_final.csv</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4111f1126af29f97325e4743c92cf22f5fb412a9262530eb5df87d5be8c9de8e</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>81</v>
+      </c>
+      <c r="K3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0c3f70a1-2e88-42a5-93b3-798bdc09e68d</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>12</v>
+      </c>
+      <c r="S3" t="n">
+        <v>81</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>trained_full_dataset</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>kmeans</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>kmeans</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>KMeans</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>kmeans</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>kmeans</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>clustering</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2026-02-27T14:09:06.793297</t>
+        </is>
+      </c>
+      <c r="AO3" t="n">
+        <v>17.13925120001659</v>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>fit_all</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\42d1e5bfc1a9434c8980fd2b57f3f8d8_preprocessed_1_40ded763_final</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>42d1e5bfc1a9434c8980fd2b57f3f8d8_preprocessed_1_40ded763_final_20260227_141346.joblib</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>joblib</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\artifacts\42d1e5bfc1a9434c8980fd2b57f3f8d8_preprocessed_1_40ded763_final\42d1e5bfc1a9434c8980fd2b57f3f8d8_preprocessed_1_40ded763_final_20260227_141346.joblib</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\42d1e5bfc1a9434c8980fd2b57f3f8d8_preprocessed_1_40ded763_final.csv</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4111f1126af29f97325e4743c92cf22f5fb412a9262530eb5df87d5be8c9de8e</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>81</v>
+      </c>
+      <c r="K4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>c3f5ac6e-72a6-4cfb-b346-80fda5315782</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>12</v>
+      </c>
+      <c r="S4" t="n">
+        <v>81</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>trained_full_dataset</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>kmeans</t>
+        </is>
+      </c>
+      <c r="AA4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>kmeans</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>KMeans</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>kmeans</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>kmeans</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>clustering</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>2026-02-27T14:13:48.327724</t>
+        </is>
+      </c>
+      <c r="AO4" t="n">
+        <v>23.89120319997892</v>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>fit_all</t>
         </is>
       </c>
     </row>
